--- a/public/samples/mail-merge-template.xlsx
+++ b/public/samples/mail-merge-template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -405,6 +405,7 @@
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,6 +427,9 @@
       <c r="F1" t="str">
         <v>PDF Password</v>
       </c>
+      <c r="G1" t="str">
+        <v>Attachment</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -446,6 +450,9 @@
       <c r="F2" t="str">
         <v/>
       </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -466,6 +473,9 @@
       <c r="F3" t="str">
         <v/>
       </c>
+      <c r="G3" t="str">
+        <v>john_invoice.pdf</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -486,10 +496,13 @@
       <c r="F4" t="str">
         <v>welcome123</v>
       </c>
+      <c r="G4" t="str">
+        <v>priya_offer.pdf</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>